--- a/EKG_Kalite_Yönetim_Sistemi/12_Üretim ve Malzeme Akış Yönetimi/02_MMFM2 - Kapasite ve Darboğaz Yönetimi/EKG-LOJ-MTR-03_kaynak_ve_esneklik_risk_degerlendirmesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/12_Üretim ve Malzeme Akış Yönetimi/02_MMFM2 - Kapasite ve Darboğaz Yönetimi/EKG-LOJ-MTR-03_kaynak_ve_esneklik_risk_degerlendirmesi.xlsx
@@ -838,7 +838,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-03&amp;C&amp;"Arial,Regular"&amp;11Kaynak ve Esneklik Risk Değerlendirmesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 04.09.2026
+Revizyon nedeni: Lojistik yedekleri risk matrisi kapasite, insan, malzeme ve taşıma alternatifleriyle düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -971,7 +972,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-03&amp;C&amp;"Arial,Regular"&amp;11Kaynak ve Esneklik Risk Değerlendirmesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 04.09.2026
+Revizyon nedeni: Lojistik yedekleri risk matrisi kapasite, insan, malzeme ve taşıma alternatifleriyle düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>